--- a/artfynd/A 21845-2026 artfynd.xlsx
+++ b/artfynd/A 21845-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>133852451</v>
       </c>
       <c r="B3" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133852460</v>
       </c>
       <c r="B4" t="n">
-        <v>97372</v>
+        <v>97378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>133859347</v>
       </c>
       <c r="B5" t="n">
-        <v>97372</v>
+        <v>97378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>133852452</v>
       </c>
       <c r="B6" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>133852450</v>
       </c>
       <c r="B7" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21845-2026 artfynd.xlsx
+++ b/artfynd/A 21845-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>133852451</v>
       </c>
       <c r="B3" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133852460</v>
       </c>
       <c r="B4" t="n">
-        <v>97378</v>
+        <v>97380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>133859347</v>
       </c>
       <c r="B5" t="n">
-        <v>97378</v>
+        <v>97380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>133852452</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>133852450</v>
       </c>
       <c r="B7" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21845-2026 artfynd.xlsx
+++ b/artfynd/A 21845-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133859341</v>
       </c>
       <c r="B2" t="n">
-        <v>6274</v>
+        <v>6286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>133852451</v>
       </c>
       <c r="B3" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133852460</v>
       </c>
       <c r="B4" t="n">
-        <v>97380</v>
+        <v>97408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>133859347</v>
       </c>
       <c r="B5" t="n">
-        <v>97380</v>
+        <v>97408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>133852452</v>
       </c>
       <c r="B6" t="n">
-        <v>91301</v>
+        <v>91320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>133852450</v>
       </c>
       <c r="B7" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21845-2026 artfynd.xlsx
+++ b/artfynd/A 21845-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>133852451</v>
       </c>
       <c r="B3" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133852460</v>
       </c>
       <c r="B4" t="n">
-        <v>97408</v>
+        <v>97418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>133859347</v>
       </c>
       <c r="B5" t="n">
-        <v>97408</v>
+        <v>97418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>133852452</v>
       </c>
       <c r="B6" t="n">
-        <v>91320</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>133852450</v>
       </c>
       <c r="B7" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21845-2026 artfynd.xlsx
+++ b/artfynd/A 21845-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>133852451</v>
       </c>
       <c r="B3" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133852460</v>
       </c>
       <c r="B4" t="n">
-        <v>97418</v>
+        <v>97420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>133859347</v>
       </c>
       <c r="B5" t="n">
-        <v>97418</v>
+        <v>97420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>133852452</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>133852450</v>
       </c>
       <c r="B7" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21845-2026 artfynd.xlsx
+++ b/artfynd/A 21845-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>133852451</v>
       </c>
       <c r="B3" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133852460</v>
       </c>
       <c r="B4" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>133859347</v>
       </c>
       <c r="B5" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>133852452</v>
       </c>
       <c r="B6" t="n">
-        <v>91333</v>
+        <v>91340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>133852450</v>
       </c>
       <c r="B7" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21845-2026 artfynd.xlsx
+++ b/artfynd/A 21845-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133859341</v>
+        <v>133852460</v>
       </c>
       <c r="B2" t="n">
-        <v>6286</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105336</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527290</v>
+        <v>527275</v>
       </c>
       <c r="R2" t="n">
-        <v>6638752</v>
+        <v>6638846</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133852451</v>
+        <v>133859347</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,30 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527306</v>
+        <v>527270</v>
       </c>
       <c r="R3" t="n">
-        <v>6638922</v>
+        <v>6638872</v>
       </c>
       <c r="S3" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133852460</v>
+        <v>133852450</v>
       </c>
       <c r="B4" t="n">
-        <v>97428</v>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,27 +908,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527275</v>
+        <v>527286</v>
       </c>
       <c r="R4" t="n">
-        <v>6638846</v>
+        <v>6638790</v>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133859347</v>
+        <v>133852451</v>
       </c>
       <c r="B5" t="n">
-        <v>97428</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,27 +1027,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527270</v>
+        <v>527306</v>
       </c>
       <c r="R5" t="n">
-        <v>6638872</v>
+        <v>6638922</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133852452</v>
+        <v>133859344</v>
       </c>
       <c r="B6" t="n">
-        <v>91340</v>
+        <v>92188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>3008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1181,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527232</v>
+        <v>527290</v>
       </c>
       <c r="R6" t="n">
-        <v>6638849</v>
+        <v>6638752</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,41 +1248,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133852450</v>
+        <v>133852452</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>91347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527286</v>
+        <v>527232</v>
       </c>
       <c r="R7" t="n">
-        <v>6638790</v>
+        <v>6638849</v>
       </c>
       <c r="S7" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallhögstubbe</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,6 +1363,130 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133859341</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6286</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vattuberget, Ribäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527290</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6638752</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
